--- a/XLibur.Tests/Resource/Other/Cubes/CubeFromRange-Output.xlsx
+++ b/XLibur.Tests/Resource/Other/Cubes/CubeFromRange-Output.xlsx
@@ -211,15 +211,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t>Pastry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Price</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Amount</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cake</x:t>
   </x:si>
   <x:si>
@@ -227,6 +218,15 @@
   </x:si>
   <x:si>
     <x:t>Pie</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pastry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Amount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Price</x:t>
   </x:si>
   <x:si>
     <x:t>Row Labels</x:t>
@@ -628,18 +628,18 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <x:c r="A1" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <x:c r="A2" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B2" s="0">
         <x:v>7</x:v>
@@ -650,7 +650,7 @@
     </x:row>
     <x:row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <x:c r="A3" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="0">
         <x:v>14</x:v>
@@ -661,7 +661,7 @@
     </x:row>
     <x:row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <x:c r="A4" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="0">
         <x:v>12</x:v>

--- a/XLibur.Tests/Resource/Other/Cubes/CubeFromRange-Output.xlsx
+++ b/XLibur.Tests/Resource/Other/Cubes/CubeFromRange-Output.xlsx
@@ -620,87 +620,77 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{85B18120-0F73-4C31-A836-C307E1148084}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:C4"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:sheetData>
     <x:row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="B1" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C1" s="0" t="s">
+      <x:c r="C1" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="A2" s="0" t="s">
+      <x:c r="A2" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B2" s="0">
+      <x:c r="B2">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C2" s="0">
+      <x:c r="C2">
         <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="A3" s="0" t="s">
+      <x:c r="A3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B3" s="0">
+      <x:c r="B3">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C3" s="0">
+      <x:c r="C3">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="A4" s="0" t="s">
+      <x:c r="A4" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B4" s="0">
+      <x:c r="B4">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C4" s="0">
+      <x:c r="C4">
         <x:v>35</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{C0AD9516-2EBA-49A5-B123-EFA4DD7E7834}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A3:C7"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="13.140625" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="2" max="2" width="12" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="3" max="3" width="14.855469" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <x:col min="3" max="3" width="14.855469" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="A3" s="0" t="s">
+      <x:c r="A3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="str" vm="4">
+      <x:c r="B3" t="str" vm="4">
         <x:f>CUBEMEMBER("ThisWorkbookDataModel","[Measures].[Sum of Price]")</x:f>
         <x:v>Sum of Price</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="str" vm="6">
+      <x:c r="C3" t="str" vm="6">
         <x:f>CUBEMEMBER("ThisWorkbookDataModel","[Measures].[Sum of Amount]")</x:f>
         <x:v>Sum of Amount</x:v>
       </x:c>
@@ -710,11 +700,11 @@
         <x:f>CUBEMEMBER("ThisWorkbookDataModel","[Range].[Pastry].&amp;[Baclava]")</x:f>
         <x:v>Baclava</x:v>
       </x:c>
-      <x:c r="B4" s="0" vm="13">
+      <x:c r="B4" vm="13">
         <x:f>CUBEVALUE("ThisWorkbookDataModel",$A4,B$3)</x:f>
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C4" s="0" vm="14">
+      <x:c r="C4" vm="14">
         <x:f>CUBEVALUE("ThisWorkbookDataModel",$A4,C$3)</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -724,11 +714,11 @@
         <x:f>CUBEMEMBER("ThisWorkbookDataModel","[Range].[Pastry].&amp;[Cake]")</x:f>
         <x:v>Cake</x:v>
       </x:c>
-      <x:c r="B5" s="0" vm="11">
+      <x:c r="B5" vm="11">
         <x:f>CUBEVALUE("ThisWorkbookDataModel",$A5,B$3)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C5" s="0" vm="12">
+      <x:c r="C5" vm="12">
         <x:f>CUBEVALUE("ThisWorkbookDataModel",$A5,C$3)</x:f>
         <x:v>27</x:v>
       </x:c>
@@ -738,11 +728,11 @@
         <x:f>CUBEMEMBER("ThisWorkbookDataModel","[Range].[Pastry].&amp;[Pie]")</x:f>
         <x:v>Pie</x:v>
       </x:c>
-      <x:c r="B6" s="0" vm="9">
+      <x:c r="B6" vm="9">
         <x:f>CUBEVALUE("ThisWorkbookDataModel",$A6,B$3)</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C6" s="0" vm="10">
+      <x:c r="C6" vm="10">
         <x:f>CUBEVALUE("ThisWorkbookDataModel",$A6,C$3)</x:f>
         <x:v>35</x:v>
       </x:c>
@@ -752,20 +742,16 @@
         <x:f>CUBEMEMBER("ThisWorkbookDataModel","[Range].[Pastry].[All]","Grand Total")</x:f>
         <x:v>Grand Total</x:v>
       </x:c>
-      <x:c r="B7" s="0" vm="7">
+      <x:c r="B7" vm="7">
         <x:f>CUBEVALUE("ThisWorkbookDataModel",$A7,B$3)</x:f>
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C7" s="0" vm="8">
+      <x:c r="C7" vm="8">
         <x:f>CUBEVALUE("ThisWorkbookDataModel",$A7,C$3)</x:f>
         <x:v>65</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Other/Cubes/CubeFromRange-Output.xlsx
+++ b/XLibur.Tests/Resource/Other/Cubes/CubeFromRange-Output.xlsx
@@ -701,11 +701,11 @@
         <x:v>Baclava</x:v>
       </x:c>
       <x:c r="B4" vm="13">
-        <x:f>CUBEVALUE("ThisWorkbookDataModel",$A4,B$3)</x:f>
+        <x:f t="shared" ref="B4:C7" si="0">CUBEVALUE("ThisWorkbookDataModel",$A4,B$3)</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="C4" vm="14">
-        <x:f>CUBEVALUE("ThisWorkbookDataModel",$A4,C$3)</x:f>
+        <x:f t="shared" si="0"/>
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -715,11 +715,11 @@
         <x:v>Cake</x:v>
       </x:c>
       <x:c r="B5" vm="11">
-        <x:f>CUBEVALUE("ThisWorkbookDataModel",$A5,B$3)</x:f>
+        <x:f t="shared" si="0"/>
         <x:v>7</x:v>
       </x:c>
       <x:c r="C5" vm="12">
-        <x:f>CUBEVALUE("ThisWorkbookDataModel",$A5,C$3)</x:f>
+        <x:f t="shared" si="0"/>
         <x:v>27</x:v>
       </x:c>
     </x:row>
@@ -729,11 +729,11 @@
         <x:v>Pie</x:v>
       </x:c>
       <x:c r="B6" vm="9">
-        <x:f>CUBEVALUE("ThisWorkbookDataModel",$A6,B$3)</x:f>
+        <x:f t="shared" si="0"/>
         <x:v>12</x:v>
       </x:c>
       <x:c r="C6" vm="10">
-        <x:f>CUBEVALUE("ThisWorkbookDataModel",$A6,C$3)</x:f>
+        <x:f t="shared" si="0"/>
         <x:v>35</x:v>
       </x:c>
     </x:row>
@@ -743,11 +743,11 @@
         <x:v>Grand Total</x:v>
       </x:c>
       <x:c r="B7" vm="7">
-        <x:f>CUBEVALUE("ThisWorkbookDataModel",$A7,B$3)</x:f>
+        <x:f t="shared" si="0"/>
         <x:v>33</x:v>
       </x:c>
       <x:c r="C7" vm="8">
-        <x:f>CUBEVALUE("ThisWorkbookDataModel",$A7,C$3)</x:f>
+        <x:f t="shared" si="0"/>
         <x:v>65</x:v>
       </x:c>
     </x:row>

--- a/XLibur.Tests/Resource/Other/Cubes/CubeFromRange-Output.xlsx
+++ b/XLibur.Tests/Resource/Other/Cubes/CubeFromRange-Output.xlsx
@@ -679,7 +679,7 @@
   <x:cols>
     <x:col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
     <x:col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <x:col min="3" max="3" width="14.855469" bestFit="1" customWidth="1"/>
+    <x:col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="3" spans="1:3" x14ac:dyDescent="0.25">
